--- a/converted/oylik/2026-08/Elektr Podstansiyalar.xlsx
+++ b/converted/oylik/2026-08/Elektr Podstansiyalar.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
   <si>
     <t>Podstansiyalar Avgust Holatiga Ko'ra</t>
   </si>
@@ -46,6 +46,15 @@
     <t>Podstansiya Nomi (manba)</t>
   </si>
   <si>
+    <t>Umumiy oqim (podstansiya faylida)</t>
+  </si>
+  <si>
+    <t>Foydali oqim (podstansiya faylida)</t>
+  </si>
+  <si>
+    <t>Yo’qotish (podstansiya faylida)</t>
+  </si>
+  <si>
     <t>Manzil (manba)</t>
   </si>
   <si>
@@ -58,6 +67,9 @@
     <t>Ma'sul xodim (manba)</t>
   </si>
   <si>
+    <t>Eslatma</t>
+  </si>
+  <si>
     <t>Manba (fayl, qator)</t>
   </si>
   <si>
@@ -112,6 +124,9 @@
     <t>110 kV</t>
   </si>
   <si>
+    <t>Quvvati (KVA) o'rnida kuchlanish (kV) yozilgan - bo'sh qoldirildi</t>
+  </si>
+  <si>
     <t>chinobod/Elektr Podstansiyalar.xlsx [Avgust], 3-qator</t>
   </si>
   <si>
@@ -134,6 +149,12 @@
   </si>
   <si>
     <t>chinobod/Elektr Podstansiyalar.xlsx [Avgust], 4-qator</t>
+  </si>
+  <si>
+    <t>Oltinko'l</t>
+  </si>
+  <si>
+    <t>transformatorlar.xlsx [Avgust], 41-qator</t>
   </si>
 </sst>
 </file>
@@ -552,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:S7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
@@ -561,10 +582,10 @@
     <col min="6" max="7" width="16" style="2" customWidth="1"/>
     <col min="8" max="8" width="18" style="1" customWidth="1"/>
     <col min="9" max="9" width="22" customWidth="1"/>
-    <col min="10" max="15" width="26" customWidth="1"/>
+    <col min="10" max="19" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" ht="30" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -582,8 +603,12 @@
       <c r="M1"/>
       <c r="N1"/>
       <c r="O1"/>
+      <c r="P1"/>
+      <c r="Q1"/>
+      <c r="R1"/>
+      <c r="S1"/>
     </row>
-    <row r="2" ht="45" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" ht="45" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -629,22 +654,34 @@
       <c r="O2" s="5" t="s">
         <v>15</v>
       </c>
+      <c r="P2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="S2" s="5" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B3" s="1">
-        <v>704146</v>
+        <v>1630310.079761</v>
       </c>
       <c r="C3" s="1">
-        <v>612366</v>
+        <v>1393612.044924</v>
       </c>
       <c r="D3" s="1">
-        <v>95778</v>
+        <v>236698.034837</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F3" s="2">
         <v>40.829053</v>
@@ -656,30 +693,39 @@
         <v>10000</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
-        <v>19</v>
-      </c>
-      <c r="O3" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="K3">
+        <v>704146</v>
+      </c>
+      <c r="L3">
+        <v>612366</v>
+      </c>
+      <c r="M3">
+        <v>95778</v>
+      </c>
+      <c r="S3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B4" s="1">
-        <v>6971295</v>
+        <v>7429334.920239</v>
       </c>
       <c r="C4" s="1">
-        <v>6034352</v>
+        <v>6466691.942076</v>
       </c>
       <c r="D4" s="1">
-        <v>936942</v>
+        <v>962642.978163</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F4" s="2">
         <v>40.901381</v>
@@ -691,33 +737,42 @@
         <v>80000</v>
       </c>
       <c r="I4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J4" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" t="s">
-        <v>25</v>
-      </c>
-      <c r="O4" t="s">
-        <v>26</v>
+        <v>28</v>
+      </c>
+      <c r="K4">
+        <v>6971295</v>
+      </c>
+      <c r="L4">
+        <v>6034352</v>
+      </c>
+      <c r="M4">
+        <v>936942</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>29</v>
+      </c>
+      <c r="S4" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B5" s="1">
-        <v>3243000</v>
+        <v>4283878.754554</v>
       </c>
       <c r="C5" s="1">
-        <v>2724120</v>
+        <v>3571961.371019</v>
       </c>
       <c r="D5" s="1">
-        <v>518880</v>
+        <v>711917.383535</v>
       </c>
       <c r="E5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F5" s="2">
         <v>40.866486</v>
@@ -726,39 +781,51 @@
         <v>71.968873</v>
       </c>
       <c r="I5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J5" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" t="s">
-        <v>27</v>
-      </c>
-      <c r="L5" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5">
+        <v>3243000</v>
+      </c>
+      <c r="L5">
+        <v>2724120</v>
+      </c>
+      <c r="M5">
+        <v>518880</v>
+      </c>
+      <c r="N5" t="s">
         <v>31</v>
       </c>
-      <c r="M5" t="s">
-        <v>32</v>
-      </c>
       <c r="O5" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="P5" t="s">
+        <v>36</v>
+      </c>
+      <c r="R5" t="s">
+        <v>37</v>
+      </c>
+      <c r="S5" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B6" s="1">
-        <v>2646000</v>
+        <v>3047310.490747</v>
       </c>
       <c r="C6" s="1">
-        <v>2222640</v>
+        <v>2528302.019713</v>
       </c>
       <c r="D6" s="1">
-        <v>423360</v>
+        <v>519008.471034</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F6" s="2">
         <v>40.850754</v>
@@ -767,27 +834,65 @@
         <v>72.04806</v>
       </c>
       <c r="I6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J6" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6">
+        <v>2646000</v>
+      </c>
+      <c r="L6">
+        <v>2222640</v>
+      </c>
+      <c r="M6">
+        <v>423360</v>
+      </c>
+      <c r="N6" t="s">
+        <v>42</v>
+      </c>
+      <c r="O6" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6" t="s">
+        <v>44</v>
+      </c>
+      <c r="R6" t="s">
         <v>37</v>
       </c>
-      <c r="L6" t="s">
-        <v>38</v>
-      </c>
-      <c r="M6" t="s">
-        <v>39</v>
-      </c>
-      <c r="O6" t="s">
-        <v>40</v>
+      <c r="S6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="1">
+        <v>656814.754698</v>
+      </c>
+      <c r="C7" s="1">
+        <v>545699.609268</v>
+      </c>
+      <c r="D7" s="1">
+        <v>111115.145431</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="S7" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
